--- a/Result/profitability/1110.xlsx
+++ b/Result/profitability/1110.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.13</v>
       </c>
       <c r="M2" t="n">
-        <v>0.12375</v>
+        <v>0.11625</v>
       </c>
       <c r="N2" t="n">
-        <v>16.1725</v>
+        <v>15.66125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,13 +780,13 @@
         <v>0.1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0925</v>
+        <v>0.115</v>
       </c>
       <c r="N3" t="n">
-        <v>15.2275</v>
+        <v>15.25875</v>
       </c>
       <c r="O3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="n">
         <v>1</v>
@@ -798,7 +798,7 @@
         <v>0</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>0.04</v>
       </c>
       <c r="M4" t="n">
-        <v>0.08375</v>
+        <v>0.11</v>
       </c>
       <c r="N4" t="n">
-        <v>14.485</v>
+        <v>14.905</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.25</v>
       </c>
       <c r="M5" t="n">
-        <v>0.04250000000000001</v>
+        <v>0.07999999999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>14.34</v>
+        <v>14.745</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.06</v>
       </c>
       <c r="M6" t="n">
-        <v>0.05125</v>
+        <v>0.06125</v>
       </c>
       <c r="N6" t="n">
-        <v>13.99875</v>
+        <v>14.04625</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.12</v>
       </c>
       <c r="M7" t="n">
-        <v>0.04000000000000001</v>
+        <v>0.0675</v>
       </c>
       <c r="N7" t="n">
-        <v>13.32125</v>
+        <v>13.58</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.16</v>
       </c>
       <c r="M8" t="n">
-        <v>0.05125</v>
+        <v>0.08125</v>
       </c>
       <c r="N8" t="n">
-        <v>12.9325</v>
+        <v>13.31</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1403,7 +1403,7 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
         <v>0</v>
@@ -1518,7 +1518,7 @@
         <v>-0.18</v>
       </c>
       <c r="M9" t="n">
-        <v>0.02250000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="N9" t="n">
         <v>12.97875</v>
@@ -1645,7 +1645,7 @@
         <v>0.03</v>
       </c>
       <c r="M10" t="n">
-        <v>0.01000000000000001</v>
+        <v>0.01</v>
       </c>
       <c r="N10" t="n">
         <v>12.265</v>
@@ -1772,7 +1772,7 @@
         <v>0.04</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002500000000000005</v>
+        <v>0.002500000000000001</v>
       </c>
       <c r="N11" t="n">
         <v>11.83625</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1110</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>685</v>
+      </c>
+      <c r="D75" t="n">
+        <v>566</v>
+      </c>
+      <c r="E75" t="n">
+        <v>119</v>
+      </c>
+      <c r="F75" t="n">
+        <v>17.35</v>
+      </c>
+      <c r="G75" t="n">
+        <v>68</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>9.96%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>117</v>
+      </c>
+      <c r="J75" t="n">
+        <v>186</v>
+      </c>
+      <c r="K75" t="n">
+        <v>168</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.29</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.14375</v>
+      </c>
+      <c r="N75" t="n">
+        <v>16.32125</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="X75" t="n">
+        <v>4.799999999999999</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.020000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.2107466852756457</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-30</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>3.240000000000002</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2296243798724311</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
